--- a/ParaBank Bug Report.xlsx
+++ b/ParaBank Bug Report.xlsx
@@ -1,11 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29512"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29328"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C18FC244-2DA7-4A53-984F-D1A837650ACD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tifam\Desktop\Parabank Testing Project\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1202432B-36B9-4770-ADD2-8C1CA6DE0052}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Abdelrahman" sheetId="1" r:id="rId1"/>
@@ -880,7 +885,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="16">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1497,21 +1502,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J34"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="23.42578125" style="6" customWidth="1"/>
-    <col min="2" max="2" width="19.7109375" style="8" customWidth="1"/>
-    <col min="3" max="3" width="24.7109375" style="8" customWidth="1"/>
-    <col min="4" max="4" width="22.140625" style="8" customWidth="1"/>
-    <col min="5" max="5" width="23.5703125" style="8" customWidth="1"/>
-    <col min="6" max="6" width="17.28515625" style="8" customWidth="1"/>
-    <col min="7" max="7" width="13.42578125" style="8" customWidth="1"/>
-    <col min="8" max="8" width="23.7109375" style="19" customWidth="1"/>
-    <col min="9" max="9" width="23.140625" style="6" customWidth="1"/>
-    <col min="10" max="10" width="23.7109375" style="8" customWidth="1"/>
+    <col min="1" max="1" width="23.44140625" style="6" customWidth="1"/>
+    <col min="2" max="2" width="19.6640625" style="8" customWidth="1"/>
+    <col min="3" max="3" width="24.6640625" style="8" customWidth="1"/>
+    <col min="4" max="4" width="22.109375" style="8" customWidth="1"/>
+    <col min="5" max="5" width="23.5546875" style="8" customWidth="1"/>
+    <col min="6" max="6" width="17.33203125" style="8" customWidth="1"/>
+    <col min="7" max="7" width="13.44140625" style="8" customWidth="1"/>
+    <col min="8" max="8" width="23.6640625" style="19" customWidth="1"/>
+    <col min="9" max="9" width="23.109375" style="6" customWidth="1"/>
+    <col min="10" max="10" width="23.6640625" style="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="18.75">
+    <row r="1" spans="1:10" ht="18" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
@@ -1543,7 +1548,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="18">
+    <row r="2" spans="1:10" ht="18" x14ac:dyDescent="0.3">
       <c r="A2" s="12"/>
       <c r="B2" s="10" t="s">
         <v>10</v>
@@ -1552,7 +1557,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="57.75">
+    <row r="3" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
         <v>12</v>
       </c>
@@ -1581,7 +1586,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="57.75">
+    <row r="4" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="s">
         <v>20</v>
       </c>
@@ -1610,7 +1615,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="57.75">
+    <row r="5" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A5" s="12" t="s">
         <v>27</v>
       </c>
@@ -1639,7 +1644,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="57.75">
+    <row r="6" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A6" s="12" t="s">
         <v>31</v>
       </c>
@@ -1668,7 +1673,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="57.75">
+    <row r="7" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A7" s="12" t="s">
         <v>35</v>
       </c>
@@ -1697,7 +1702,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="57.75">
+    <row r="8" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A8" s="12" t="s">
         <v>39</v>
       </c>
@@ -1726,7 +1731,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="101.25">
+    <row r="9" spans="1:10" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A9" s="12" t="s">
         <v>43</v>
       </c>
@@ -1755,7 +1760,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="57.75">
+    <row r="10" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A10" s="12" t="s">
         <v>48</v>
       </c>
@@ -1784,7 +1789,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="57.75">
+    <row r="11" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A11" s="6" t="s">
         <v>54</v>
       </c>
@@ -1813,7 +1818,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="57.75">
+    <row r="12" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A12" s="14" t="s">
         <v>59</v>
       </c>
@@ -1842,7 +1847,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="13" spans="1:10" ht="130.5">
+    <row r="13" spans="1:10" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A13" s="12" t="s">
         <v>64</v>
       </c>
@@ -1871,13 +1876,13 @@
         <v>70</v>
       </c>
     </row>
-    <row r="14" spans="1:10" ht="18">
+    <row r="14" spans="1:10" ht="18" x14ac:dyDescent="0.3">
       <c r="A14" s="12"/>
       <c r="B14" s="10" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="15" spans="1:10" ht="72.75">
+    <row r="15" spans="1:10" ht="72" x14ac:dyDescent="0.3">
       <c r="A15" s="12" t="s">
         <v>72</v>
       </c>
@@ -1906,7 +1911,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="16" spans="1:10" ht="115.5">
+    <row r="16" spans="1:10" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A16" s="12" t="s">
         <v>80</v>
       </c>
@@ -1935,7 +1940,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="72.75">
+    <row r="17" spans="1:9" ht="72" x14ac:dyDescent="0.3">
       <c r="A17" s="12" t="s">
         <v>87</v>
       </c>
@@ -1964,7 +1969,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="87">
+    <row r="18" spans="1:9" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A18" s="6" t="s">
         <v>93</v>
       </c>
@@ -1993,7 +1998,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="20" spans="1:9" ht="101.25">
+    <row r="20" spans="1:9" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A20" s="6" t="s">
         <v>99</v>
       </c>
@@ -2022,7 +2027,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="21" spans="1:9" ht="101.25">
+    <row r="21" spans="1:9" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A21" s="13" t="s">
         <v>105</v>
       </c>
@@ -2051,7 +2056,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="22" spans="1:9" ht="101.25">
+    <row r="22" spans="1:9" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A22" s="13" t="s">
         <v>110</v>
       </c>
@@ -2080,7 +2085,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="23" spans="1:9" ht="101.25">
+    <row r="23" spans="1:9" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A23" s="13" t="s">
         <v>115</v>
       </c>
@@ -2109,7 +2114,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="24" spans="1:9" ht="101.25">
+    <row r="24" spans="1:9" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A24" s="13" t="s">
         <v>120</v>
       </c>
@@ -2138,7 +2143,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="25" spans="1:9" ht="115.5">
+    <row r="25" spans="1:9" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A25" s="13" t="s">
         <v>124</v>
       </c>
@@ -2167,7 +2172,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="26" spans="1:9" ht="115.5">
+    <row r="26" spans="1:9" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A26" s="13" t="s">
         <v>128</v>
       </c>
@@ -2196,11 +2201,11 @@
         <v>132</v>
       </c>
     </row>
-    <row r="27" spans="1:9">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="F27" s="6"/>
       <c r="G27" s="6"/>
     </row>
-    <row r="28" spans="1:9" ht="72.75">
+    <row r="28" spans="1:9" ht="72" x14ac:dyDescent="0.3">
       <c r="A28" s="6" t="s">
         <v>133</v>
       </c>
@@ -2229,7 +2234,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="29" spans="1:9" ht="72.75">
+    <row r="29" spans="1:9" ht="72" x14ac:dyDescent="0.3">
       <c r="A29" s="13" t="s">
         <v>139</v>
       </c>
@@ -2258,12 +2263,12 @@
         <v>144</v>
       </c>
     </row>
-    <row r="30" spans="1:9">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30" s="13"/>
       <c r="F30" s="6"/>
       <c r="G30" s="6"/>
     </row>
-    <row r="31" spans="1:9" ht="159">
+    <row r="31" spans="1:9" ht="144" x14ac:dyDescent="0.3">
       <c r="A31" s="6" t="s">
         <v>145</v>
       </c>
@@ -2292,7 +2297,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="32" spans="1:9" ht="72.75">
+    <row r="32" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A32" s="6" t="s">
         <v>152</v>
       </c>
@@ -2321,7 +2326,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="33" spans="1:9" ht="144.75">
+    <row r="33" spans="1:9" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A33" s="6" t="s">
         <v>158</v>
       </c>
@@ -2350,7 +2355,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="34" spans="1:9" ht="87">
+    <row r="34" spans="1:9" ht="72" x14ac:dyDescent="0.3">
       <c r="A34" s="6" t="s">
         <v>164</v>
       </c>
@@ -2392,21 +2397,21 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{870F3CA4-CA3C-4B72-A681-8FF915ED3702}">
   <dimension ref="A1:J7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="31.28515625" customWidth="1"/>
-    <col min="2" max="2" width="33.140625" customWidth="1"/>
-    <col min="3" max="3" width="41.140625" customWidth="1"/>
-    <col min="4" max="4" width="26.7109375" customWidth="1"/>
+    <col min="1" max="1" width="31.33203125" customWidth="1"/>
+    <col min="2" max="2" width="33.109375" customWidth="1"/>
+    <col min="3" max="3" width="41.109375" customWidth="1"/>
+    <col min="4" max="4" width="26.6640625" customWidth="1"/>
     <col min="5" max="5" width="34" customWidth="1"/>
-    <col min="6" max="6" width="20.28515625" customWidth="1"/>
-    <col min="7" max="7" width="19.85546875" customWidth="1"/>
-    <col min="8" max="8" width="23.7109375" customWidth="1"/>
-    <col min="9" max="9" width="26.5703125" customWidth="1"/>
-    <col min="10" max="10" width="23.7109375" customWidth="1"/>
+    <col min="6" max="6" width="20.33203125" customWidth="1"/>
+    <col min="7" max="7" width="19.88671875" customWidth="1"/>
+    <col min="8" max="8" width="23.6640625" customWidth="1"/>
+    <col min="9" max="9" width="26.5546875" customWidth="1"/>
+    <col min="10" max="10" width="23.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="18.75">
+    <row r="1" spans="1:10" ht="18" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2438,7 +2443,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="222" customHeight="1">
+    <row r="2" spans="1:10" ht="222" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="24" t="s">
         <v>169</v>
       </c>
@@ -2467,7 +2472,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="216.75" customHeight="1">
+    <row r="3" spans="1:10" ht="216.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="24" t="s">
         <v>175</v>
       </c>
@@ -2496,7 +2501,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="222.75" customHeight="1">
+    <row r="4" spans="1:10" ht="222.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="24" t="s">
         <v>181</v>
       </c>
@@ -2525,7 +2530,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="210" customHeight="1">
+    <row r="5" spans="1:10" ht="210" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="24" t="s">
         <v>187</v>
       </c>
@@ -2554,7 +2559,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="213" customHeight="1">
+    <row r="6" spans="1:10" ht="213" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="24" t="s">
         <v>193</v>
       </c>
@@ -2583,7 +2588,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="214.5" customHeight="1">
+    <row r="7" spans="1:10" ht="214.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="24" t="s">
         <v>199</v>
       </c>
@@ -2625,21 +2630,21 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03DC08E7-CB0C-4DAA-9228-37839BA72C7F}">
   <dimension ref="A1:J2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.140625" customWidth="1"/>
-    <col min="2" max="2" width="27.42578125" customWidth="1"/>
-    <col min="3" max="3" width="46.42578125" customWidth="1"/>
-    <col min="4" max="4" width="22.140625" customWidth="1"/>
-    <col min="5" max="5" width="23.5703125" customWidth="1"/>
-    <col min="6" max="6" width="17.28515625" customWidth="1"/>
-    <col min="7" max="7" width="13.42578125" customWidth="1"/>
-    <col min="8" max="8" width="23.7109375" customWidth="1"/>
-    <col min="9" max="9" width="23.140625" customWidth="1"/>
-    <col min="10" max="10" width="23.7109375" customWidth="1"/>
+    <col min="1" max="1" width="13.109375" customWidth="1"/>
+    <col min="2" max="2" width="27.44140625" customWidth="1"/>
+    <col min="3" max="3" width="46.44140625" customWidth="1"/>
+    <col min="4" max="4" width="22.109375" customWidth="1"/>
+    <col min="5" max="5" width="23.5546875" customWidth="1"/>
+    <col min="6" max="6" width="17.33203125" customWidth="1"/>
+    <col min="7" max="7" width="13.44140625" customWidth="1"/>
+    <col min="8" max="8" width="23.6640625" customWidth="1"/>
+    <col min="9" max="9" width="23.109375" customWidth="1"/>
+    <col min="10" max="10" width="23.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="18.75">
+    <row r="1" spans="1:10" ht="18" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2671,7 +2676,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="15.75">
+    <row r="2" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B2" s="4"/>
       <c r="C2" s="5"/>
       <c r="H2" s="3" t="s">
@@ -2691,21 +2696,21 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{020204B8-FB2A-4288-8477-62F86964E5FC}">
   <dimension ref="A1:J2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.140625" customWidth="1"/>
-    <col min="2" max="2" width="16.140625" customWidth="1"/>
-    <col min="3" max="3" width="24.7109375" customWidth="1"/>
-    <col min="4" max="4" width="22.140625" customWidth="1"/>
-    <col min="5" max="5" width="23.5703125" customWidth="1"/>
-    <col min="6" max="6" width="17.28515625" customWidth="1"/>
-    <col min="7" max="7" width="13.42578125" customWidth="1"/>
-    <col min="8" max="8" width="23.7109375" customWidth="1"/>
-    <col min="9" max="9" width="23.140625" customWidth="1"/>
-    <col min="10" max="10" width="23.7109375" customWidth="1"/>
+    <col min="1" max="1" width="13.109375" customWidth="1"/>
+    <col min="2" max="2" width="16.109375" customWidth="1"/>
+    <col min="3" max="3" width="24.6640625" customWidth="1"/>
+    <col min="4" max="4" width="22.109375" customWidth="1"/>
+    <col min="5" max="5" width="23.5546875" customWidth="1"/>
+    <col min="6" max="6" width="17.33203125" customWidth="1"/>
+    <col min="7" max="7" width="13.44140625" customWidth="1"/>
+    <col min="8" max="8" width="23.6640625" customWidth="1"/>
+    <col min="9" max="9" width="23.109375" customWidth="1"/>
+    <col min="10" max="10" width="23.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="18.75">
+    <row r="1" spans="1:10" ht="18" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2737,7 +2742,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="15.75">
+    <row r="2" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="H2" s="3" t="s">
         <v>11</v>
       </c>
@@ -2755,21 +2760,21 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9565BB6C-B179-4B4F-8313-FB5EC841EFF7}">
   <dimension ref="A1:J2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.140625" customWidth="1"/>
-    <col min="2" max="2" width="16.140625" customWidth="1"/>
-    <col min="3" max="3" width="24.7109375" customWidth="1"/>
-    <col min="4" max="4" width="22.140625" customWidth="1"/>
-    <col min="5" max="5" width="23.5703125" customWidth="1"/>
-    <col min="6" max="6" width="17.28515625" customWidth="1"/>
-    <col min="7" max="7" width="13.42578125" customWidth="1"/>
-    <col min="8" max="8" width="23.7109375" customWidth="1"/>
-    <col min="9" max="9" width="23.140625" customWidth="1"/>
-    <col min="10" max="10" width="23.7109375" customWidth="1"/>
+    <col min="1" max="1" width="13.109375" customWidth="1"/>
+    <col min="2" max="2" width="16.109375" customWidth="1"/>
+    <col min="3" max="3" width="24.6640625" customWidth="1"/>
+    <col min="4" max="4" width="22.109375" customWidth="1"/>
+    <col min="5" max="5" width="23.5546875" customWidth="1"/>
+    <col min="6" max="6" width="17.33203125" customWidth="1"/>
+    <col min="7" max="7" width="13.44140625" customWidth="1"/>
+    <col min="8" max="8" width="23.6640625" customWidth="1"/>
+    <col min="9" max="9" width="23.109375" customWidth="1"/>
+    <col min="10" max="10" width="23.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="18.75">
+    <row r="1" spans="1:10" ht="18" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2801,7 +2806,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="15.75">
+    <row r="2" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="H2" s="3" t="s">
         <v>11</v>
       </c>
